--- a/docs/triton-learning/cards/triton-lesson-08-grouped-gemm-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-08-grouped-gemm-oral.xlsx
@@ -36,68 +36,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">请用约 60–90 秒向面试官讲清：Triton 官方教程的 grouped GEMM kernel 怎样用一次发射算完一组尺寸不同的矩阵乘法？它相对逐个调用换来了什么、付出了什么？教程的实现有什么边界？</t>
+          <t xml:space="preserve">请用约 60–90 秒向面试官讲清：Triton 3.7.1 官方教程的 grouped GEMM kernel 怎样用一次发射算完一组尺寸不同的矩阵乘法？它相对逐个调用换来了什么、付出了什么？教程的实现有什么边界？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：把每个问题按同样的块大小切开，所有块首尾相接排成一条队列，只发射一次、固定数量的 CTA，每个 CTA 按步长领块；换来的是只付一次发射开销、小问题也能把 SM 填满。
 • [T#B#怎样交给 kernel]：矩阵个数运行时才知道，所以矩阵不是参数：地址、尺寸和行步长都存在设备上的表里，kernel 读出整数再转成指针。
-• [T#B#怎样领任务]：第 p 个 CTA 处理第 p、p+NUM_SM…… 号块，用各问题块数的前缀和找到这一块属于哪个问题，块内就是普通的分块矩阵乘。
+• [T#B#怎样领任务]：第 p 个 CTA 处理第 p、p+NUM_SM…… 号块，用各问题块数的前缀和找到这一块属于哪个问题。
 • [T#B#代价]：每个 CTA 要扫描问题表；整组共用一种块大小；调度只均分块数，各问题 K 不同时工作量不均衡。
-• [T#B#教程的假定]：教程假定尺寸是块的整数倍，不满足时会越界读写；真实的 MoE 只有行数参差，用行方向的 mask 或 TMA 描述符处理。
+• [T#B#教程的假定]：教程假定尺寸都是块的整数倍，不满足时会越界读写；真实的 MoE 只有行数参差，要补的主要是 M 方向的不满块。
 [T#B,!c47f17#边界]：它适合数量多、规模小、K 相近的问题；问题很少且每个都能占满所有 SM 时，逐个调用就够了。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">说出块排成队列、固定数量的 CTA 按步长领取；说明矩阵经设备上的地址表、尺寸表和行步长表交给 kernel；说出两项收益：一次发射、小问题也能填满 SM；至少说出两项代价：扫描、共用块大小、工作量不均；指出满块假定这一边界和真实 MoE 的处理办法</t>
+          <t xml:space="preserve">说出块排成队列、固定数量的 CTA 按步长领取；说明矩阵经设备上的地址表、尺寸表和行步长表交给 kernel；说出两项收益：一次发射、小问题也能填满 SM；至少说出两项代价：扫描、共用块大小、工作量不均；指出满块假定这一边界，以及真实 MoE 里只有行数参差</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 全流程串联</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 真实规模与综合验收（口述题）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">请用约 60–90 秒回答面试官：一个 Triton kernel 的指针是运行时从地址表读出来的。要让它把数据从显存搬进共享内存时既快又不出错，对齐保证、异步拷贝和 TMA 描述符各起什么作用，各自在什么条件下失效？</t>
+          <t xml:space="preserve">请用约 60–90 秒回答面试官：在 Triton 3.7.1 的 NVIDIA 后端上，一个 kernel 的指针是运行时从地址表读出来的。要让它把数据从显存搬进共享内存时既快又不出错，对齐保证、异步拷贝和 TMA 描述符各起什么作用，各自在什么条件下失效？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：编译器知道得越多，搬得越快：不知道是否对齐时每次只搬 2 字节，有了对齐保证就用 16 字节的异步拷贝并做流水，有了描述符就整块交给硬件。
-• [T#B#对齐保证]：tl.multiple_of 是不被检查的保证。它要求首地址和行步长的字节数都是 16 的倍数；不成立时是未定义行为，没有报错。
-• [T#B#降档]：行步长只是 8 或 4 字节的倍数时，可以如实把保证降到 8 或 4，指令变多但流水还在；TMA 没有这个余地。
-• [T#B#mask 的影响]：只加行方向的 mask 不影响异步拷贝；N、K 方向也加 mask 后退回逐个元素的读。
-• [T#B#TMA]：描述符带着真实形状，界外的读补 0、界外不写，不再要求整块；但要对齐、要全局暂存区，没有 TMA 的设备上会被改写成指针加 mask。
+• [T#B#对齐保证]：tl.multiple_of 是不被检查的保证，要求首地址和每一行的行首都是 16 字节的倍数；不成立属未定义行为，可能报错、读错，也可能碰巧正确。
+• [T#B#降档]：行步长只是 8 或 4 字节的倍数时，可以如实把保证降到 8 或 4，条数变多但流水还在；TMA 没有这个余地。
+• [T#B#mask 的影响]：只加行方向的 mask 不影响异步拷贝；N、K 方向也加 mask 后，编译器推不出 mask 在一段里保持不变，退回逐个元素的读。
+• [T#B#TMA]：描述符带着真实形状，界外读补 0、界外不写，不再要求整块；但行步长必须 16 字节对齐，设备端现场创建还要全局暂存区。
 [T#B,!c47f17#边界]：异步拷贝只有读这一个方向，写回显存的异步搬运只有 TMA 才有。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明 tl.multiple_of 是不被检查的保证，以及它成立的两个条件；说出保证可以如实降到 8 或 4，而 TMA 不能降档；说明行方向的 mask 保住异步拷贝，三个方向的 mask 不行；说明描述符怎样处理界外，以及没有 TMA 时的回退；指出保证不成立是未定义行为，不会报错</t>
+          <t xml:space="preserve">说明 tl.multiple_of 是不被检查的保证，以及它要求每一行行首都对齐；说出保证可以如实降到 8 或 4，而 TMA 不能降档；说明行方向的 mask 保住异步拷贝，三个方向的 mask 不行；说明描述符怎样处理界外，以及它换来的对齐和暂存要求；指出保证不成立属未定义行为，结果不可预期，不能指望报错</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 数据搬运串联</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 对齐保证、异步拷贝与 TMA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">请用约 60–90 秒回答面试官：你写了一个从地址表取矩阵的 grouped GEMM kernel。它对输入有哪些假定？这些假定由谁来保证？你怎样测试它，哪些错误是数值测试测不出来的？</t>
+          <t xml:space="preserve">请用约 60–90 秒回答面试官：你用 Triton 3.7.1 写了一个从地址表取矩阵的 grouped GEMM kernel。它对输入有哪些假定？这些假定由谁来保证？你怎样测试它，哪些错误是数值测试测不出来的？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：kernel 只拿到表里的整数，自己验证不了任何假定，所以全部由包装函数检查；测试要同时覆盖数值、越界和参数检查三类。
-• [T#B#假定与检查]：dtype、行内连续、同一设备、A 和 B 的对齐，每项检查对应 kernel 的一条假定；没有假定的检查，例如对输出的对齐检查，只会拒绝本来能处理的输入。
-• [T#B#漏掉的后果]：漏掉检查通常不报错：类型不对时结果是 NaN，行内不连续时读到错位的数据，都是静默的。
+• [T#B#假定与检查]：dtype、行内连续、A 和 B 的对齐，每项检查对应 kernel 的一条假定；没有假定的检查，例如对输出的对齐检查，只会拒绝本来能处理的输入。
+• [T#B#漏掉的后果]：漏掉检查通常不报错：类型不对时结果含 NaN，行内不连续时读到错位的数据，都是静默的。
 • [T#B#越界]：只比较结果发现不了越界写。把输入嵌进 NaN、输出嵌进哨兵值的缓冲区，四周各留一整块。
 • [T#B#测试的盲区]：对齐保证不成立是未定义行为，结果可能碰巧正确，只能用断言抛出 ValueError 的参数测试覆盖。
 [T#B,!c47f17#边界]：测试输入还要变换特殊情形的位置：整组共用的标志如果只按最后一个问题来定，特殊问题排在前面时才会出错。</t>
@@ -110,7 +110,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 假定与测试串联</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · A6：每项检查保护哪个假定；练习：提交、定位与测试缺口</t>
         </is>
       </c>
     </row>

--- a/docs/triton-learning/cards/triton-lesson-08-grouped-gemm-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-08-grouped-gemm-oral.xlsx
@@ -69,7 +69,7 @@
       <c r="B3" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：编译器知道得越多，搬得越快：不知道是否对齐时每次只搬 2 字节，有了对齐保证就用 16 字节的异步拷贝并做流水，有了描述符就整块交给硬件。
-• [T#B#对齐保证]：tl.multiple_of 是不被检查的保证，要求首地址和每一行的行首都是 16 字节的倍数；不成立属未定义行为，可能报错、读错，也可能碰巧正确。
+• [T#B#对齐保证]：tl.multiple_of 是不被检查的保证，要求首地址和每一行的行首都是 16 字节的倍数；不成立属未定义行为：H100 上实测直接报 misaligned address，进程的 CUDA 随之不能再用，其他后端未实测。
 • [T#B#降档]：行步长只是 8 或 4 字节的倍数时，可以如实把保证降到 8 或 4，条数变多但流水还在；TMA 没有这个余地。
 • [T#B#mask 的影响]：只加行方向的 mask 不影响异步拷贝；N、K 方向也加 mask 后，编译器推不出 mask 在一段里保持不变，退回逐个元素的读。
 • [T#B#TMA]：描述符带着真实形状，界外读补 0、界外不写，不再要求整块；但行步长必须 16 字节对齐，设备端现场创建还要全局暂存区。
@@ -78,7 +78,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明 tl.multiple_of 是不被检查的保证，以及它要求每一行行首都对齐；说出保证可以如实降到 8 或 4，而 TMA 不能降档；说明行方向的 mask 保住异步拷贝，三个方向的 mask 不行；说明描述符怎样处理界外，以及它换来的对齐和暂存要求；指出保证不成立属未定义行为，结果不可预期，不能指望报错</t>
+          <t xml:space="preserve">说明 tl.multiple_of 是不被检查的保证，以及它要求每一行行首都对齐；说出保证可以如实降到 8 或 4，而 TMA 不能降档；说明行方向的 mask 保住异步拷贝，三个方向的 mask 不行；说明描述符怎样处理界外，以及它换来的对齐和暂存要求；指出保证不成立属未定义行为：H100 上实测报错且进程不能再用，其他后端未实测，不能把它当作检查</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -99,7 +99,7 @@
 • [T#B#假定与检查]：dtype、行内连续、A 和 B 的对齐，每项检查对应 kernel 的一条假定；没有假定的检查，例如对输出的对齐检查，只会拒绝本来能处理的输入。
 • [T#B#漏掉的后果]：漏掉检查通常不报错：类型不对时结果含 NaN，行内不连续时读到错位的数据，都是静默的。
 • [T#B#越界]：只比较结果发现不了越界写。把输入嵌进 NaN、输出嵌进哨兵值的缓冲区，四周各留一整块。
-• [T#B#测试的盲区]：对齐保证不成立是未定义行为，结果可能碰巧正确，只能用断言抛出 ValueError 的参数测试覆盖。
+• [T#B#测试的盲区]：对齐保证不成立是未定义行为：CPU 解释器上照样算对，H100 上直接报 misaligned address 并让进程的 CUDA 不能再用，所以只能用断言抛出 ValueError 的参数测试覆盖。
 [T#B,!c47f17#边界]：测试输入还要变换特殊情形的位置：整组共用的标志如果只按最后一个问题来定，特殊问题排在前面时才会出错。</t>
         </is>
       </c>
